--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J657"/>
+  <dimension ref="A1:J661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24070,7 +24070,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>344.25</v>
+        <v>343.49</v>
       </c>
       <c r="C657" t="n">
         <v>337.78</v>
@@ -24094,6 +24094,150 @@
         <v>337.56</v>
       </c>
       <c r="J657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:19:55+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="C658" t="n">
+        <v>338.29</v>
+      </c>
+      <c r="D658" t="n">
+        <v>328</v>
+      </c>
+      <c r="E658" t="n">
+        <v>326.1</v>
+      </c>
+      <c r="F658" t="n">
+        <v>330.67</v>
+      </c>
+      <c r="G658" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="H658" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="I658" t="n">
+        <v>337.76</v>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="C659" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="D659" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="E659" t="n">
+        <v>326.05</v>
+      </c>
+      <c r="F659" t="n">
+        <v>330.91</v>
+      </c>
+      <c r="G659" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="H659" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="I659" t="n">
+        <v>338.89</v>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:51+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>342.49</v>
+      </c>
+      <c r="C660" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="D660" t="n">
+        <v>326.95</v>
+      </c>
+      <c r="E660" t="n">
+        <v>325.78</v>
+      </c>
+      <c r="F660" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="G660" t="n">
+        <v>330.63</v>
+      </c>
+      <c r="H660" t="n">
+        <v>333.44</v>
+      </c>
+      <c r="I660" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>341.75</v>
+      </c>
+      <c r="C661" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="D661" t="n">
+        <v>326.4</v>
+      </c>
+      <c r="E661" t="n">
+        <v>325.74</v>
+      </c>
+      <c r="F661" t="n">
+        <v>330.24</v>
+      </c>
+      <c r="G661" t="n">
+        <v>330.48</v>
+      </c>
+      <c r="H661" t="n">
+        <v>333.24</v>
+      </c>
+      <c r="I661" t="n">
+        <v>338.08</v>
+      </c>
+      <c r="J661" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24110,7 +24254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B744"/>
+  <dimension ref="A1:B748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31553,6 +31697,46 @@
       </c>
       <c r="B744" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -31721,28 +31905,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3679427602496794</v>
+        <v>-0.3622360528224261</v>
       </c>
       <c r="J2" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K2" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3640080549383468</v>
+        <v>0.3572919133315172</v>
       </c>
       <c r="M2" t="n">
-        <v>2.616070354184429</v>
+        <v>2.624538075333577</v>
       </c>
       <c r="N2" t="n">
-        <v>10.5917007775302</v>
+        <v>10.64175327411344</v>
       </c>
       <c r="O2" t="n">
-        <v>3.254489326688629</v>
+        <v>3.262170025322628</v>
       </c>
       <c r="P2" t="n">
-        <v>348.1964870927615</v>
+        <v>348.1250788444527</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31803,28 +31987,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3878322120452604</v>
+        <v>-0.383932459334651</v>
       </c>
       <c r="J3" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K3" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4058642931758903</v>
+        <v>0.4026795811588325</v>
       </c>
       <c r="M3" t="n">
-        <v>2.434562214574425</v>
+        <v>2.43645135079011</v>
       </c>
       <c r="N3" t="n">
-        <v>9.859550622555334</v>
+        <v>9.858178486741616</v>
       </c>
       <c r="O3" t="n">
-        <v>3.139992137339731</v>
+        <v>3.139773636226283</v>
       </c>
       <c r="P3" t="n">
-        <v>344.4994541886773</v>
+        <v>344.4506653081184</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31885,28 +32069,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2728588322426262</v>
+        <v>-0.2782902627337046</v>
       </c>
       <c r="J4" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K4" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1209303877896815</v>
+        <v>0.1261296292092389</v>
       </c>
       <c r="M4" t="n">
-        <v>3.914763473524001</v>
+        <v>3.915201364095747</v>
       </c>
       <c r="N4" t="n">
-        <v>24.23418462354105</v>
+        <v>24.19163268393216</v>
       </c>
       <c r="O4" t="n">
-        <v>4.922822830809682</v>
+        <v>4.918499027542057</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6907666447642</v>
+        <v>338.7587306952085</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31967,28 +32151,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5002232482382021</v>
+        <v>-0.5080415919679055</v>
       </c>
       <c r="J5" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K5" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5322719800638683</v>
+        <v>0.5378747776030295</v>
       </c>
       <c r="M5" t="n">
-        <v>2.435596257935175</v>
+        <v>2.456424021033636</v>
       </c>
       <c r="N5" t="n">
-        <v>9.845824380586572</v>
+        <v>9.998072740547798</v>
       </c>
       <c r="O5" t="n">
-        <v>3.137805663291876</v>
+        <v>3.161972919009238</v>
       </c>
       <c r="P5" t="n">
-        <v>345.3338783096543</v>
+        <v>345.4317055503765</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32045,28 +32229,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4529896304885886</v>
+        <v>-0.4549301768866732</v>
       </c>
       <c r="J6" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K6" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4926496128515311</v>
+        <v>0.4976630025965352</v>
       </c>
       <c r="M6" t="n">
-        <v>2.439080786425003</v>
+        <v>2.432867328887776</v>
       </c>
       <c r="N6" t="n">
-        <v>9.462609742312495</v>
+        <v>9.418647949876592</v>
       </c>
       <c r="O6" t="n">
-        <v>3.076135520797563</v>
+        <v>3.068981581873145</v>
       </c>
       <c r="P6" t="n">
-        <v>344.2533698023522</v>
+        <v>344.2776520215971</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32123,28 +32307,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5709064311365684</v>
+        <v>-0.5732758130489576</v>
       </c>
       <c r="J7" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K7" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6790285714897217</v>
+        <v>0.683014659092124</v>
       </c>
       <c r="M7" t="n">
-        <v>2.108512811071581</v>
+        <v>2.107052844501853</v>
       </c>
       <c r="N7" t="n">
-        <v>6.898787296817123</v>
+        <v>6.876629948210923</v>
       </c>
       <c r="O7" t="n">
-        <v>2.626554263063515</v>
+        <v>2.622332920933367</v>
       </c>
       <c r="P7" t="n">
-        <v>347.7950468648548</v>
+        <v>347.8246939703757</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32205,28 +32389,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5375995686375435</v>
+        <v>-0.53638378519689</v>
       </c>
       <c r="J8" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K8" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5412086698774421</v>
+        <v>0.5431709928317694</v>
       </c>
       <c r="M8" t="n">
-        <v>2.612930375479773</v>
+        <v>2.603710302711806</v>
       </c>
       <c r="N8" t="n">
-        <v>10.97066208318667</v>
+        <v>10.90957035429886</v>
       </c>
       <c r="O8" t="n">
-        <v>3.312198980011115</v>
+        <v>3.302963874204328</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9536950115536</v>
+        <v>346.9384831374538</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32287,28 +32471,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4042303204044668</v>
+        <v>-0.4029622345786626</v>
       </c>
       <c r="J9" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K9" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3774249533699788</v>
+        <v>0.3788564344938724</v>
       </c>
       <c r="M9" t="n">
-        <v>2.701208363445037</v>
+        <v>2.690963030113701</v>
       </c>
       <c r="N9" t="n">
-        <v>12.06933742859609</v>
+        <v>12.00287485150154</v>
       </c>
       <c r="O9" t="n">
-        <v>3.474095195672693</v>
+        <v>3.464516539360368</v>
       </c>
       <c r="P9" t="n">
-        <v>348.2084176631932</v>
+        <v>348.1925508056811</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32350,7 +32534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J657"/>
+  <dimension ref="A1:J661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66473,7 +66657,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>-45.216475799618046,170.88808454696007</t>
+          <t>-45.2164701993232,170.88807899338173</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -66512,6 +66696,214 @@
         </is>
       </c>
       <c r="J657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:19:55+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-45.216473294223015,170.88808206246438</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-45.216802579915615,170.88731660277466</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-45.21699603950265,170.886462652382</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-45.21724653599021,170.88562797405618</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-45.21777646852325,170.88505880627937</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>-45.21833045345556,170.8845904235556</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>-45.21892711973997,170.88426297380477</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>-45.21952474716477,170.88395906064193</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-45.216468504497065,170.88807731269375</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-45.21679713406286,170.88731212415698</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-45.21699193885567,170.88646003273328</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-45.21724617226512,170.8856275993466</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>-45.21777775424211,170.8850612614275</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>-45.21833235465039,170.88459548221965</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>-45.218929049413376,170.8842690053332</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>-45.21952894051647,170.88397216773836</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:51+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-45.21646283051377,170.88807168604342</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-45.216789276475,170.88730566215298</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-45.216987428143945,170.8864571511201</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-45.21724420814964,170.88562557591493</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-45.217775825663786,170.88505757870533</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>-45.21833100268965,170.8845918849474</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>-45.21892778770389,170.88426506164149</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>-45.21952749325364,170.88396764405</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-45.21645737759451,170.88806627861428</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-45.21678274145118,170.88730028781433</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-45.21698291743212,170.88645426950737</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-45.21724391716956,170.88562527614727</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-45.217774164943485,170.88505440747255</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>-45.218330368958014,170.88459019872607</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>-45.218927045521774,170.8842627418229</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>-45.21952593466274,170.88396277238584</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J661"/>
+  <dimension ref="A1:J665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24238,6 +24238,150 @@
         <v>338.08</v>
       </c>
       <c r="J661" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>340.86</v>
+      </c>
+      <c r="C662" t="n">
+        <v>335</v>
+      </c>
+      <c r="D662" t="n">
+        <v>325.35</v>
+      </c>
+      <c r="E662" t="n">
+        <v>324.94</v>
+      </c>
+      <c r="F662" t="n">
+        <v>329.52</v>
+      </c>
+      <c r="G662" t="n">
+        <v>329.97</v>
+      </c>
+      <c r="H662" t="n">
+        <v>332.48</v>
+      </c>
+      <c r="I662" t="n">
+        <v>337.21</v>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="C663" t="n">
+        <v>334.41</v>
+      </c>
+      <c r="D663" t="n">
+        <v>325</v>
+      </c>
+      <c r="E663" t="n">
+        <v>324.7</v>
+      </c>
+      <c r="F663" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="G663" t="n">
+        <v>329.63</v>
+      </c>
+      <c r="H663" t="n">
+        <v>332.19</v>
+      </c>
+      <c r="I663" t="n">
+        <v>336.95</v>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>340.09</v>
+      </c>
+      <c r="C664" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="D664" t="n">
+        <v>324.96</v>
+      </c>
+      <c r="E664" t="n">
+        <v>324.96</v>
+      </c>
+      <c r="F664" t="n">
+        <v>328.71</v>
+      </c>
+      <c r="G664" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="H664" t="n">
+        <v>332.27</v>
+      </c>
+      <c r="I664" t="n">
+        <v>337.1</v>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:16+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>339.97</v>
+      </c>
+      <c r="C665" t="n">
+        <v>334.06</v>
+      </c>
+      <c r="D665" t="n">
+        <v>324.63</v>
+      </c>
+      <c r="E665" t="n">
+        <v>324.82</v>
+      </c>
+      <c r="F665" t="n">
+        <v>327.77</v>
+      </c>
+      <c r="G665" t="n">
+        <v>329.36</v>
+      </c>
+      <c r="H665" t="n">
+        <v>332.26</v>
+      </c>
+      <c r="I665" t="n">
+        <v>337.18</v>
+      </c>
+      <c r="J665" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24254,7 +24398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B748"/>
+  <dimension ref="A1:B753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31737,6 +31881,56 @@
       </c>
       <c r="B748" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -31905,28 +32099,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3622360528224261</v>
+        <v>-0.3597306316891185</v>
       </c>
       <c r="J2" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K2" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3572919133315172</v>
+        <v>0.3565552671740936</v>
       </c>
       <c r="M2" t="n">
-        <v>2.624538075333577</v>
+        <v>2.619311244325982</v>
       </c>
       <c r="N2" t="n">
-        <v>10.64175327411344</v>
+        <v>10.60042490381664</v>
       </c>
       <c r="O2" t="n">
-        <v>3.262170025322628</v>
+        <v>3.255829372650944</v>
       </c>
       <c r="P2" t="n">
-        <v>348.1250788444527</v>
+        <v>348.0936377493103</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31987,28 +32181,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.383932459334651</v>
+        <v>-0.3834949235823572</v>
       </c>
       <c r="J3" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K3" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4026795811588325</v>
+        <v>0.4051843219062737</v>
       </c>
       <c r="M3" t="n">
-        <v>2.43645135079011</v>
+        <v>2.423720414073002</v>
       </c>
       <c r="N3" t="n">
-        <v>9.858178486741616</v>
+        <v>9.800157442279948</v>
       </c>
       <c r="O3" t="n">
-        <v>3.139773636226283</v>
+        <v>3.130520314944458</v>
       </c>
       <c r="P3" t="n">
-        <v>344.4506653081184</v>
+        <v>344.4451785423708</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32069,28 +32263,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2782902627337046</v>
+        <v>-0.2864185743844288</v>
       </c>
       <c r="J4" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K4" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1261296292092389</v>
+        <v>0.1329813959312508</v>
       </c>
       <c r="M4" t="n">
-        <v>3.915201364095747</v>
+        <v>3.928652899342937</v>
       </c>
       <c r="N4" t="n">
-        <v>24.19163268393216</v>
+        <v>24.27861597799389</v>
       </c>
       <c r="O4" t="n">
-        <v>4.918499027542057</v>
+        <v>4.927333556599745</v>
       </c>
       <c r="P4" t="n">
-        <v>338.7587306952085</v>
+        <v>338.8607532480968</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32151,28 +32345,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5080415919679055</v>
+        <v>-0.5169566442862107</v>
       </c>
       <c r="J5" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K5" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5378747776030295</v>
+        <v>0.5428086667811112</v>
       </c>
       <c r="M5" t="n">
-        <v>2.456424021033636</v>
+        <v>2.482479684105753</v>
       </c>
       <c r="N5" t="n">
-        <v>9.998072740547798</v>
+        <v>10.21747298908236</v>
       </c>
       <c r="O5" t="n">
-        <v>3.161972919009238</v>
+        <v>3.196478216581862</v>
       </c>
       <c r="P5" t="n">
-        <v>345.4317055503765</v>
+        <v>345.5435983016881</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32229,28 +32423,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4549301768866732</v>
+        <v>-0.4591431253872195</v>
       </c>
       <c r="J6" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K6" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4976630025965352</v>
+        <v>0.5037546853054423</v>
       </c>
       <c r="M6" t="n">
-        <v>2.432867328887776</v>
+        <v>2.436809567017866</v>
       </c>
       <c r="N6" t="n">
-        <v>9.418647949876592</v>
+        <v>9.426653256227191</v>
       </c>
       <c r="O6" t="n">
-        <v>3.068981581873145</v>
+        <v>3.070285533338421</v>
       </c>
       <c r="P6" t="n">
-        <v>344.2776520215971</v>
+        <v>344.3305390585518</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32307,28 +32501,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5732758130489576</v>
+        <v>-0.5768588229123141</v>
       </c>
       <c r="J7" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K7" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L7" t="n">
-        <v>0.683014659092124</v>
+        <v>0.6870406960403179</v>
       </c>
       <c r="M7" t="n">
-        <v>2.107052844501853</v>
+        <v>2.111358192610808</v>
       </c>
       <c r="N7" t="n">
-        <v>6.876629948210923</v>
+        <v>6.88063503875616</v>
       </c>
       <c r="O7" t="n">
-        <v>2.622332920933367</v>
+        <v>2.623096460055589</v>
       </c>
       <c r="P7" t="n">
-        <v>347.8246939703757</v>
+        <v>347.8696677897639</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32389,28 +32583,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.53638378519689</v>
+        <v>-0.536608341718719</v>
       </c>
       <c r="J8" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K8" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5431709928317694</v>
+        <v>0.5465529703459137</v>
       </c>
       <c r="M8" t="n">
-        <v>2.603710302711806</v>
+        <v>2.588863583830183</v>
       </c>
       <c r="N8" t="n">
-        <v>10.90957035429886</v>
+        <v>10.84409169015745</v>
       </c>
       <c r="O8" t="n">
-        <v>3.302963874204328</v>
+        <v>3.2930368491952</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9384831374538</v>
+        <v>346.9413019973507</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32471,28 +32665,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4029622345786626</v>
+        <v>-0.403245544369475</v>
       </c>
       <c r="J9" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K9" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3788564344938724</v>
+        <v>0.3822035655564919</v>
       </c>
       <c r="M9" t="n">
-        <v>2.690963030113701</v>
+        <v>2.67598780632078</v>
       </c>
       <c r="N9" t="n">
-        <v>12.00287485150154</v>
+        <v>11.93091790351324</v>
       </c>
       <c r="O9" t="n">
-        <v>3.464516539360368</v>
+        <v>3.454116081360503</v>
       </c>
       <c r="P9" t="n">
-        <v>348.1925508056811</v>
+        <v>348.1961059019789</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32534,7 +32728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J661"/>
+  <dimension ref="A1:J665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66909,6 +67103,214 @@
         </is>
       </c>
     </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-45.216450819353454,170.888059775086</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-45.21677698440618,170.8872955532789</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-45.216974306073034,170.88644876824793</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-45.21723809756792,170.88561928079503</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-45.2177703077863,170.88504704202944</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>-45.218328214270265,170.88458446557394</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>-45.2189242252293,170.88425392651288</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>-45.219522706152354,170.8839526810824</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-45.216446324379056,170.8880553176124</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-45.216772394329645,170.8872917784473</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-45.21697143561994,170.88644693449513</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-45.21723635168736,170.88561748218956</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-45.217767789919584,170.88504223403237</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>-45.218326777811605,170.88458064347273</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>-45.2189231490649,170.8842505627764</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>-45.21952174130999,170.8839496652908</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-45.21644514536935,170.88805414843912</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-45.216771382956836,170.88729094670484</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-45.216971107568156,170.8864467249234</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-45.21723824305796,170.88561943067882</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-45.21776596848395,170.8850387559071</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>-45.21832597508465,170.88457850759272</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>-45.218923445937854,170.8842514907037</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>-45.219522297949815,170.88395140517056</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:16+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>-45.21644426111206,170.8880532715592</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>-45.21676967140283,170.88728953914068</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>-45.216968401140925,170.88644499595668</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>-45.21723722462765,170.88561838149226</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>-45.2177609327496,170.88502913991488</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>-45.218325637094345,170.88457760827487</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>-45.21892340882872,170.88425137471276</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>-45.2195225948244,170.88395233310644</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0478/nzd0478.xlsx
+++ b/data/nzd0478/nzd0478.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J665"/>
+  <dimension ref="A1:J668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24382,6 +24382,114 @@
         <v>337.18</v>
       </c>
       <c r="J665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:13+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>338.67</v>
+      </c>
+      <c r="C666" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="D666" t="n">
+        <v>323.15</v>
+      </c>
+      <c r="E666" t="n">
+        <v>324.34</v>
+      </c>
+      <c r="F666" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="G666" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="H666" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="I666" t="n">
+        <v>336.87</v>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>339.07</v>
+      </c>
+      <c r="C667" t="n">
+        <v>333.47</v>
+      </c>
+      <c r="D667" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="E667" t="n">
+        <v>325.37</v>
+      </c>
+      <c r="F667" t="n">
+        <v>328.03</v>
+      </c>
+      <c r="G667" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="H667" t="n">
+        <v>332.19</v>
+      </c>
+      <c r="I667" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>339.07</v>
+      </c>
+      <c r="C668" t="n">
+        <v>333.47</v>
+      </c>
+      <c r="D668" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="E668" t="n">
+        <v>325.32</v>
+      </c>
+      <c r="F668" t="n">
+        <v>327.89</v>
+      </c>
+      <c r="G668" t="n">
+        <v>328.76</v>
+      </c>
+      <c r="H668" t="n">
+        <v>331.29</v>
+      </c>
+      <c r="I668" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="J668" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24398,7 +24506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B753"/>
+  <dimension ref="A1:B757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31931,6 +32039,46 @@
       </c>
       <c r="B753" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -32099,28 +32247,28 @@
         <v>0.0471</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3597306316891185</v>
+        <v>-0.3591701368511896</v>
       </c>
       <c r="J2" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K2" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3565552671740936</v>
+        <v>0.3580065805673379</v>
       </c>
       <c r="M2" t="n">
-        <v>2.619311244325982</v>
+        <v>2.609871139991953</v>
       </c>
       <c r="N2" t="n">
-        <v>10.60042490381664</v>
+        <v>10.55441209175624</v>
       </c>
       <c r="O2" t="n">
-        <v>3.255829372650944</v>
+        <v>3.248755468137951</v>
       </c>
       <c r="P2" t="n">
-        <v>348.0936377493103</v>
+        <v>348.0865750824597</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32181,28 +32329,28 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3834949235823572</v>
+        <v>-0.3841311272696639</v>
       </c>
       <c r="J3" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K3" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4051843219062737</v>
+        <v>0.4082514648167835</v>
       </c>
       <c r="M3" t="n">
-        <v>2.423720414073002</v>
+        <v>2.415987628498758</v>
       </c>
       <c r="N3" t="n">
-        <v>9.800157442279948</v>
+        <v>9.758037462995373</v>
       </c>
       <c r="O3" t="n">
-        <v>3.130520314944458</v>
+        <v>3.123785758177947</v>
       </c>
       <c r="P3" t="n">
-        <v>344.4451785423708</v>
+        <v>344.4531912415094</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32263,28 +32411,28 @@
         <v>0.1531</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2864185743844288</v>
+        <v>-0.294319671550266</v>
       </c>
       <c r="J4" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K4" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1329813959312508</v>
+        <v>0.1390767551967632</v>
       </c>
       <c r="M4" t="n">
-        <v>3.928652899342937</v>
+        <v>3.947205464916978</v>
       </c>
       <c r="N4" t="n">
-        <v>24.27861597799389</v>
+        <v>24.46484701556786</v>
       </c>
       <c r="O4" t="n">
-        <v>4.927333556599745</v>
+        <v>4.946195205970732</v>
       </c>
       <c r="P4" t="n">
-        <v>338.8607532480968</v>
+        <v>338.9602803541379</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32345,28 +32493,28 @@
         <v>0.1453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5169566442862107</v>
+        <v>-0.5232892359568614</v>
       </c>
       <c r="J5" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K5" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5428086667811112</v>
+        <v>0.5466168796038313</v>
       </c>
       <c r="M5" t="n">
-        <v>2.482479684105753</v>
+        <v>2.50069920200906</v>
       </c>
       <c r="N5" t="n">
-        <v>10.21747298908236</v>
+        <v>10.3623904219955</v>
       </c>
       <c r="O5" t="n">
-        <v>3.196478216581862</v>
+        <v>3.219066700457681</v>
       </c>
       <c r="P5" t="n">
-        <v>345.5435983016881</v>
+        <v>345.6233603844272</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32423,28 +32571,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4591431253872195</v>
+        <v>-0.4632487354527882</v>
       </c>
       <c r="J6" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K6" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5037546853054423</v>
+        <v>0.5084650597777332</v>
       </c>
       <c r="M6" t="n">
-        <v>2.436809567017866</v>
+        <v>2.443861732887177</v>
       </c>
       <c r="N6" t="n">
-        <v>9.426653256227191</v>
+        <v>9.464895088506735</v>
       </c>
       <c r="O6" t="n">
-        <v>3.070285533338421</v>
+        <v>3.076506962206771</v>
       </c>
       <c r="P6" t="n">
-        <v>344.3305390585518</v>
+        <v>344.382249989411</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32501,28 +32649,28 @@
         <v>0.1204</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5768588229123141</v>
+        <v>-0.5800607849507188</v>
       </c>
       <c r="J7" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K7" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6870406960403179</v>
+        <v>0.6899508574423048</v>
       </c>
       <c r="M7" t="n">
-        <v>2.111358192610808</v>
+        <v>2.116994120768497</v>
       </c>
       <c r="N7" t="n">
-        <v>6.88063503875616</v>
+        <v>6.898480286934768</v>
       </c>
       <c r="O7" t="n">
-        <v>2.623096460055589</v>
+        <v>2.626495818944848</v>
       </c>
       <c r="P7" t="n">
-        <v>347.8696677897639</v>
+        <v>347.9100002851076</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32583,28 +32731,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.536608341718719</v>
+        <v>-0.5372422020711577</v>
       </c>
       <c r="J8" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K8" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5465529703459137</v>
+        <v>0.5494576548870183</v>
       </c>
       <c r="M8" t="n">
-        <v>2.588863583830183</v>
+        <v>2.579571975377883</v>
       </c>
       <c r="N8" t="n">
-        <v>10.84409169015745</v>
+        <v>10.79780966625196</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2930368491952</v>
+        <v>3.286002079465557</v>
       </c>
       <c r="P8" t="n">
-        <v>346.9413019973507</v>
+        <v>346.9492879596932</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32665,28 +32813,28 @@
         <v>0.0601</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.403245544369475</v>
+        <v>-0.4036606342412694</v>
       </c>
       <c r="J9" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K9" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3822035655564919</v>
+        <v>0.3849181164451472</v>
       </c>
       <c r="M9" t="n">
-        <v>2.67598780632078</v>
+        <v>2.666400526626886</v>
       </c>
       <c r="N9" t="n">
-        <v>11.93091790351324</v>
+        <v>11.87931558494629</v>
       </c>
       <c r="O9" t="n">
-        <v>3.454116081360503</v>
+        <v>3.446638302019272</v>
       </c>
       <c r="P9" t="n">
-        <v>348.1961059019789</v>
+        <v>348.2013364257359</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32728,7 +32876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J665"/>
+  <dimension ref="A1:J668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67311,6 +67459,162 @@
         </is>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:13+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-45.2164346816577,170.88804377202834</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-45.21676368096367,170.8872846126669</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-45.216956263224596,170.88643724180483</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>-45.2172337328665,170.88561478428161</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>-45.21775718273414,170.88502197907073</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>-45.21832327116201,170.88457131305003</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>-45.21892177602741,170.88424627111277</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>-45.219521444435394,170.88394873735493</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-45.216437629182195,170.88804669496056</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-45.2167650813261,170.88728576431</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-45.21695380283609,170.8864356700177</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-45.21724122560383,170.8856225032967</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-45.21776232561237,170.88503179965724</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-45.218325383601616,170.88457693378646</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-45.2189231490649,170.8842505627764</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>-45.219523782322575,170.8839560448501</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-45.216437629182195,170.88804669496056</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-45.2167650813261,170.88728576431</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-45.21695380283609,170.8864356700177</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-45.217240861878736,170.8856221285872</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-45.21776157560935,170.88503036748827</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-45.21832310216683,170.88457086339113</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-45.2189198092437,170.88424012359502</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-45.21951895811044,170.88394096589255</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
